--- a/public/sap-reporting/expansion-150-downloads/EXT-QM09-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-QM09-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R7bc643e2db364024"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R04d91c9e963b4aec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R2fec18fa3f7a4be8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R0248c8d3a47d4dd4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R176c5d5881494915"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R9a0a9212ae6a4db8"/>
   </x:sheets>
 </x:workbook>
 </file>
